--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_187_R19.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_187_R19.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.300800000000001</v>
+        <v>7.2638</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3423</v>
+        <v>4.4733</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9585</v>
+        <v>2.7904</v>
       </c>
       <c r="G2" t="n">
         <v>4.7376</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>2.978</v>
+        <v>1.941</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9109</v>
+        <v>1.042</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0671</v>
+        <v>0.899</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1107</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>S. JOVIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7517</v>
+        <v>4.071</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5645</v>
+        <v>1.3049</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1872</v>
+        <v>2.7661</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5927</v>
+        <v>2.7936</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9769</v>
+        <v>1.5857</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6158</v>
+        <v>1.2079</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4132</v>
+        <v>2.7043</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0524</v>
+        <v>1.6504</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6391</v>
+        <v>1.0539</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1794</v>
+        <v>0.0893</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0755</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2549</v>
+        <v>0.154</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>3.159</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3986</v>
+        <v>-0.0077</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7604</v>
+        <v>0.731</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4735</v>
+        <v>4.0435</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9747</v>
+        <v>1.8135</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4988</v>
+        <v>2.23</v>
       </c>
       <c r="G4" t="n">
         <v>3.0527</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6502</v>
+        <v>0.2201</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0351</v>
+        <v>-0.1964</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6853</v>
+        <v>0.4165</v>
       </c>
       <c r="V4" t="n">
         <v>1.4665</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. JOVIC</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7501</v>
+        <v>3.6969</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7151</v>
+        <v>0.3417</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0349</v>
+        <v>3.3552</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7936</v>
+        <v>1.5927</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5857</v>
+        <v>0.9769</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2079</v>
+        <v>0.6158</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7043</v>
+        <v>0.4132</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6504</v>
+        <v>1.0524</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0539</v>
+        <v>-0.6391</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0893</v>
+        <v>1.1794</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0755</v>
       </c>
       <c r="O5" t="n">
-        <v>0.154</v>
+        <v>1.2549</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4024</v>
+        <v>2.1042</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5975</v>
+        <v>1.1758</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9999</v>
+        <v>0.9285</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3783</v>
+        <v>3.0326</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2995</v>
+        <v>3.2562</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0788</v>
+        <v>-0.2237</v>
       </c>
       <c r="G6" t="n">
         <v>1.431</v>
@@ -922,13 +922,13 @@
         <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5556</v>
+        <v>1.2098</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6765</v>
+        <v>0.6332</v>
       </c>
       <c r="U6" t="n">
-        <v>0.879</v>
+        <v>0.5766</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5361</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8424</v>
+        <v>2.0191</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8839</v>
+        <v>1.8589</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0415</v>
+        <v>0.1602</v>
       </c>
       <c r="G7" t="n">
         <v>1.5483</v>
@@ -1000,13 +1000,13 @@
         <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7187</v>
+        <v>0.458</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9709</v>
+        <v>0.0042</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2522</v>
+        <v>0.4538</v>
       </c>
       <c r="V7" t="n">
         <v>-2.5387</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4455</v>
+        <v>1.1174</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6839</v>
+        <v>0.0552</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1294</v>
+        <v>1.0622</v>
       </c>
       <c r="G8" t="n">
         <v>1.9676</v>
@@ -1078,13 +1078,13 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9137</v>
+        <v>-0.2418</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0455</v>
+        <v>-0.3064</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1318</v>
+        <v>0.0646</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1365</v>
+        <v>0.207</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4531</v>
+        <v>-1.3784</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3166</v>
+        <v>1.5855</v>
       </c>
       <c r="G9" t="n">
         <v>-1.105</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2634</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9709</v>
+        <v>-0.8962</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2926</v>
+        <v>-0.0237</v>
       </c>
       <c r="V9" t="n">
         <v>1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1575</v>
+        <v>-0.0059</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0011</v>
+        <v>0.1169</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1564</v>
+        <v>-0.1228</v>
       </c>
       <c r="G10" t="n">
         <v>0.052</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2095</v>
+        <v>-0.058</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4587</v>
+        <v>-0.2064</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2247</v>
+        <v>-0.1068</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.234</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0848</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2116</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5395</v>
+        <v>-0.405</v>
       </c>
       <c r="V11" t="n">
         <v>0.1418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4211</v>
+        <v>-1.7237</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1737</v>
+        <v>-1.7452</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2474</v>
+        <v>0.0214</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4899</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7352</v>
+        <v>-1.0378</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9709</v>
+        <v>-0.5423</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7644</v>
+        <v>-0.4955</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8197</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>22.7685</v>
+        <v>23.5153</v>
       </c>
       <c r="E13" t="n">
-        <v>9.243499999999999</v>
+        <v>9.9902</v>
       </c>
       <c r="F13" t="n">
         <v>13.5249</v>
@@ -1468,13 +1468,13 @@
         <v>19.7161</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6931</v>
+        <v>3.4397</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3516000000000001</v>
+        <v>0.3953</v>
       </c>
       <c r="U13" t="n">
-        <v>3.0443</v>
+        <v>3.044499999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5387</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6829</v>
+        <v>2.2117</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5713</v>
+        <v>1.3354</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1116</v>
+        <v>0.8763</v>
       </c>
       <c r="G14" t="n">
         <v>1.5487</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7631</v>
+        <v>0.2919</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2715</v>
+        <v>0.0356</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4916</v>
+        <v>0.2563</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7886</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0843</v>
+        <v>2.0013</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3938</v>
+        <v>2.7476</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3095</v>
+        <v>-0.7464</v>
       </c>
       <c r="G15" t="n">
         <v>1.1884</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3387</v>
+        <v>-0.4217</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.963</v>
+        <v>-0.6091</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6243</v>
+        <v>0.1874</v>
       </c>
       <c r="V15" t="n">
         <v>1.4665</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>G. LAVI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.355</v>
+        <v>-0.5942</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5465</v>
+        <v>-1.4788</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9015</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2375</v>
+        <v>-0.6355</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1909</v>
+        <v>0.3818</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4283</v>
+        <v>-1.0172</v>
       </c>
       <c r="J16" t="n">
-        <v>1.117</v>
+        <v>-0.3388</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5783</v>
+        <v>0.5714</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5386</v>
+        <v>-0.9102</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.2966</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7692</v>
+        <v>-0.1896</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1103</v>
+        <v>-0.107</v>
       </c>
       <c r="P16" t="n">
         <v>-0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9436</v>
+        <v>0.5052</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5351</v>
+        <v>0.0198</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4086</v>
+        <v>0.4854</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. LAVI</t>
+          <t>L. WALKER IV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8973</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7147</v>
+        <v>-0.0354</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8174</v>
+        <v>-0.7635</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6355</v>
+        <v>-1.567</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3818</v>
+        <v>-0.6601</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0172</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3388</v>
+        <v>-1.5023</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5714</v>
+        <v>0.0336</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.9102</v>
+        <v>-1.5359</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2966</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1896</v>
+        <v>-0.6938</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.107</v>
+        <v>0.6291</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2021</v>
+        <v>-0.232</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2161</v>
+        <v>-0.1415</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4182</v>
+        <v>-0.0905</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. WALKER IV</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9333</v>
+        <v>-1.2986</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0354</v>
+        <v>-0.3971</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8979</v>
+        <v>-0.9015</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.567</v>
+        <v>0.2375</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6601</v>
+        <v>-0.1909</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9068000000000001</v>
+        <v>0.4283</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5023</v>
+        <v>1.117</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0336</v>
+        <v>0.5783</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5359</v>
+        <v>0.5386</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6938</v>
+        <v>-0.7692</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6291</v>
+        <v>-0.1103</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3664</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1415</v>
+        <v>-0.4086</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2249</v>
+        <v>0.4086</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6083</v>
+        <v>1.214</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3171</v>
+        <v>-2.2772</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2654</v>
+        <v>0.4398</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5826</v>
+        <v>-2.717</v>
       </c>
       <c r="G19" t="n">
         <v>-4.7819</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4648</v>
+        <v>-0.4953</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4604</v>
+        <v>-0.3653</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0044</v>
+        <v>-0.13</v>
       </c>
       <c r="V19" t="n">
         <v>1.6083</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2483</v>
+        <v>-3.2147</v>
       </c>
       <c r="E20" t="n">
         <v>-3.3193</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.1046</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3301</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1307</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1766</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2737</v>
+        <v>0.3073</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0681</v>
+        <v>-3.5256</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6059</v>
+        <v>-0.7427</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4623</v>
+        <v>-2.783</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7503</v>
+        <v>-2.2618</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4357</v>
+        <v>-2.138</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3145</v>
+        <v>-0.1237</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5391</v>
+        <v>-0.6921</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7527</v>
+        <v>-0.729</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7863</v>
+        <v>0.0368</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2112</v>
+        <v>-1.5696</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-1.4091</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4718</v>
+        <v>-0.1605</v>
       </c>
       <c r="P21" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5162</v>
+        <v>-0.8</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0668</v>
+        <v>-0.4991</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4494</v>
+        <v>-0.3009</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0336</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.0336</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1991</v>
+        <v>-3.9166</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2145</v>
+        <v>-1.4879</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9846</v>
+        <v>-2.4287</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2618</v>
+        <v>-1.7503</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.138</v>
+        <v>-1.4357</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1237</v>
+        <v>-0.3145</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6921</v>
+        <v>-1.5391</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.729</v>
+        <v>-0.7527</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0368</v>
+        <v>-0.7863</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5696</v>
+        <v>-0.2112</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4091</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1605</v>
+        <v>0.4718</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4734</v>
+        <v>-0.3646</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9709</v>
+        <v>0.0512</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5026</v>
+        <v>-0.4158</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-2.0336</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6083</v>
+        <v>-2.0336</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6461</v>
+        <v>-5.1578</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6063</v>
+        <v>-5.2524</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0398</v>
+        <v>0.0946</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9394</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.5072</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4323</v>
+        <v>-0.0784</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5632</v>
+        <v>-0.4288</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.8711</v>
+        <v>-6.1976</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.806</v>
+        <v>-5.3341</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0651</v>
+        <v>-0.8635</v>
       </c>
       <c r="G24" t="n">
         <v>-5.2046</v>
@@ -2326,13 +2326,13 @@
         <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4734</v>
+        <v>-0.8</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3443</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1291</v>
+        <v>0.0725</v>
       </c>
       <c r="V24" t="n">
         <v>2.8223</v>
@@ -2362,10 +2362,10 @@
         <v>-22.7682</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.5251</v>
+        <v>-13.5249</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.243299999999998</v>
+        <v>-9.243499999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-14.496</v>
@@ -2404,13 +2404,13 @@
         <v>11.5978</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.6929</v>
+        <v>-2.693000000000001</v>
       </c>
       <c r="T25" t="n">
         <v>-3.0445</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3515999999999998</v>
+        <v>0.3515000000000002</v>
       </c>
       <c r="V25" t="n">
         <v>2.5388</v>
